--- a/benchmark_results.xlsx
+++ b/benchmark_results.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Benchmark Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Main Variants" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Qwen Ablations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="StableLM Ablations" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +30,19 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
     </font>
-    <font/>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -44,14 +51,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="001F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,20 +108,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -452,17 +544,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,37 +568,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Backbone</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Init Mode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ScienceQA</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>TextVQA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>GQA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>POPE</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>MME (Perc.)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>MME (Cog.)</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>MME (Total)</t>
+          <t>POPE (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>MME Perc.</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MME Cog.</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MME Total</t>
         </is>
       </c>
     </row>
@@ -513,21 +623,36 @@
           <t>MoE-LLaVA-1.8B×4 (Paper)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Official paper result</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>63.1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="G2" s="3" t="n">
         <v>61.5</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="H2" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n">
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n">
         <v>1291.6</v>
       </c>
     </row>
@@ -537,419 +662,2020 @@
           <t>MoE-LLaVA-2.7B×4 (Paper)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Phi2</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Official paper result</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>68.5</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>51.4</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>61.4</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>86.3</v>
       </c>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n">
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n">
         <v>1423</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>phi2_author</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Phi2</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>random/no_KD</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Author replica</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>88.97</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1378.9</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>306.8</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>1685.7</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Qwen Author</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>phi2_student_final</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Phi2</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>teacher_kd</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Full student KD</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>70.76000000000001</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>51.69</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>88.52</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>1399.2</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>271.1</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>1670.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>phi_entropy</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Phi2</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>topk_entropy_loss w=0.03</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>71.20999999999999</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>60.28</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>88.18000000000001</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1370.2</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>308.2</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>1678.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>phi_TS</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Phi2</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>TS Schedule</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>59.08</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>89.20999999999999</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1346.3</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>315.4</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>1661.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>phi_entropy_topk_var</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Phi2</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>topk_entropy_loss+var w=0.03</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>60.42</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1349.3</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>286.4</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>1635.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>qwen_author</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>random/no_KD</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Author replica</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>63.52</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="F9" s="9" t="n">
         <v>48.51</v>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>55.31</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="F5" s="5" t="n">
+      <c r="G9" s="9" t="n">
+        <v>61.96</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="I9" s="9" t="n">
         <v>1325.3</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="J9" s="9" t="n">
         <v>247.5</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="K9" s="9" t="n">
         <v>1572.8</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Qwen Student</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>qwen_student</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>teacher_kd</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Full student KD</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>61.8</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="F10" s="9" t="n">
         <v>48.08</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="G10" s="9" t="n">
         <v>61.93</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="F6" s="5" t="n">
+      <c r="H10" s="9" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="I10" s="9" t="n">
         <v>1310.9</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="J10" s="9" t="n">
         <v>242.9</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="K10" s="9" t="n">
         <v>1553.8</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Qwen TS</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>qwen_entropy</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>topk_entropy_loss w=0.03</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>61.88</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>87.94</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>1323.7</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>240</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>1563.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>qwen_TS</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>TS Schedule</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>62.72</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="F12" s="9" t="n">
         <v>48.89</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="G12" s="9" t="n">
         <v>61.83</v>
       </c>
-      <c r="E7" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="F7" s="5" t="n">
+      <c r="H12" s="9" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="I12" s="9" t="n">
         <v>1317.2</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="J12" s="9" t="n">
         <v>244.3</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="K12" s="9" t="n">
         <v>1561.5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Qwen Entropy (w=0.01)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>48.07</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>61.73</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>1301.3</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>233.2</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>1534.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Qwen Entropy (w=0.1)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>qwen_entropy_w01</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>topk_entropy_loss w=0.1</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
         <v>62.13</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="F13" s="9" t="n">
         <v>47.98</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="G13" s="9" t="n">
         <v>61.91</v>
       </c>
-      <c r="E9" s="5" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="F9" s="5" t="n">
+      <c r="H13" s="9" t="n">
+        <v>88.04000000000001</v>
+      </c>
+      <c r="I13" s="9" t="n">
         <v>1329.1</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="J13" s="9" t="n">
         <v>248.2</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="K13" s="9" t="n">
         <v>1577.3</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Phi2 Author</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>71.75</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>52.11</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>59.44</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>1378.9</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>306.8</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>1685.7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Phi2 Student</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>70.76000000000001</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>51.69</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>60.95</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>1399.2</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>271.1</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>1670.3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Phi2 TS</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>71.14</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>52.87</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>59.08</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="F13" s="5" t="n">
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>qwen_TS_schedule</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Adaptive TS Schedule</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>48.44</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>87.34999999999999</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>1319.2</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>247.1</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>1566.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>qwen_entropy_topk_var</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Qwen</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>topk_entropy_loss+var w=0.03 (ablation baseline)</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>88.14</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>1322.6</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>242.9</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>1565.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>stablelm_author</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>StableLM</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>random/no_KD</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Author replica</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>61.97</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>87.45999999999999</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>1322.3</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>229.6</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>1551.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>stablelm_student</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>StableLM</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>teacher_kd</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Full student KD</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>60.55</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>49.94</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>1356.6</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>241.8</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>1598.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>stablelm_TS</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>StableLM</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>TS Schedule</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>60.58</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>50.06</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>61.55</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>1352.9</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>224.3</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>1577.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>stablelm_entropy</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>StableLM</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>topk_entropy_loss w=0.03</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>87.87</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>1347</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>256.4</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>1603.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>stablelm_entropy_topk_aux</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>StableLM</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>topk_entropy_loss+aux_balance</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>61.91</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>88.20999999999999</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>1342.3</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>242.1</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>1584.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>stablelm_entropy_topk_var</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>StableLM</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>topk_entropy_loss+var w=0.03 (ablation baseline)</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>50.02</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>88.11</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>1346.3</v>
       </c>
-      <c r="G13" s="5" t="n">
-        <v>315.4</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>1661.7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Phi2 Entropy (w=0.01)</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>70.08</v>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>1337.1</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>272.5</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>1609.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>StableLM Author</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>59.77</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>61.97</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>1322.3</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>229.6</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>1551.9</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>StableLM TS</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>60.58</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>50.06</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>61.55</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>1352.9</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>224.3</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>1577.2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>StableLM Student</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>60.55</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>62.12</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>1356.6</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>241.8</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>1598.4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>StableLM Entropy (w=0.01)</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>50.18</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>1368.2</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>251.1</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>1619.3</v>
+      <c r="J21" s="12" t="n">
+        <v>249.3</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>1595.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>stablelm_adaptive_entropy</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>StableLM</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>no_teacher</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Margin-aware adaptive entropy gamma=2.0</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J22" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Colour legend:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Paper baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>Phi2 backbone</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>Qwen backbone</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>StableLM backbone</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Pending (eval running)</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>Qwen 1.8B Hyperparameter Ablations — topk_entropy_loss (baseline: qwen_entropy_topk_var, w_ent=0.03, lam=0.1, w_bal=0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>w_ent</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>lambda</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>w_bal</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>ScienceQA</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>TextVQA</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>GQA</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>POPE (%)</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>MME Perc.</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>MME Cog.</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>MME Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>qwen_entropy_topk_var [BASELINE]</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E3" s="25" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="F3" s="25" t="n">
+        <v>48</v>
+      </c>
+      <c r="G3" s="25" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="H3" s="25" t="n">
+        <v>88.14</v>
+      </c>
+      <c r="I3" s="25" t="n">
+        <v>1322.6</v>
+      </c>
+      <c r="J3" s="25" t="n">
+        <v>242.9</v>
+      </c>
+      <c r="K3" s="25" t="n">
+        <v>1565.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>qwen_abl_went_001</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C4" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D4" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>88.04000000000001</v>
+      </c>
+      <c r="I4" s="27" t="n">
+        <v>1329.9</v>
+      </c>
+      <c r="J4" s="27" t="n">
+        <v>242.9</v>
+      </c>
+      <c r="K4" s="27" t="n">
+        <v>1572.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>qwen_abl_went_01</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>1306.8</v>
+      </c>
+      <c r="J5" s="27" t="n">
+        <v>246.8</v>
+      </c>
+      <c r="K5" s="27" t="n">
+        <v>1553.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>qwen_abl_lam_001_w001</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>88.14</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>1317.1</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>240.7</v>
+      </c>
+      <c r="K6" s="27" t="n">
+        <v>1557.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>qwen_abl_lam_001_w01</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>61.65</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>87.77</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>1320.1</v>
+      </c>
+      <c r="J7" s="27" t="n">
+        <v>241.1</v>
+      </c>
+      <c r="K7" s="27" t="n">
+        <v>1561.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>qwen_abl_lam_1_w001</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>87.87</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>1318.9</v>
+      </c>
+      <c r="J8" s="27" t="n">
+        <v>236.1</v>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>qwen_abl_lam_1_w01</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>48</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>88.14</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>1327.7</v>
+      </c>
+      <c r="J9" s="27" t="n">
+        <v>238.6</v>
+      </c>
+      <c r="K9" s="27" t="n">
+        <v>1566.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>qwen_abl_wbal_0_w001</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C10" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>61.77</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>88.11</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>1311.6</v>
+      </c>
+      <c r="J10" s="27" t="n">
+        <v>237.9</v>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>1549.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>qwen_abl_wbal_0_w01</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>62.18</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>61.87</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>87.87</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>1319.5</v>
+      </c>
+      <c r="J11" s="27" t="n">
+        <v>237.9</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>1557.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>qwen_abl_wbal_01_w001</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>qwen_abl_wbal_01_w01</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>61.73</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>61.76</v>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>87.94</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>1333.2</v>
+      </c>
+      <c r="J13" s="27" t="n">
+        <v>250</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>1583.2</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Colour legend:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Ablation baseline (already in Main Variants sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Eval pending (running)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Loss formula:  Total = w_ent × (L_leak + lambda × L_imbal) + w_bal × L_var</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Args:  --entropy_loss_weight (w_ent)  --imbal_lam (lambda)  --balance_loss_weight (w_bal)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>StableLM 1.6B Hyperparameter Ablations — topk_entropy_loss (baseline: stablelm_entropy_topk_var, w_ent=0.03, lam=0.1, w_bal=0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>w_ent</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>lambda</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>w_bal</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>ScienceQA</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>TextVQA</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>GQA</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>POPE (%)</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>MME Perc.</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>MME Cog.</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>MME Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>stablelm_entropy_topk_var [BASELINE]</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E3" s="25" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="F3" s="25" t="n">
+        <v>50.02</v>
+      </c>
+      <c r="G3" s="25" t="n">
+        <v>61.86</v>
+      </c>
+      <c r="H3" s="25" t="n">
+        <v>88.11</v>
+      </c>
+      <c r="I3" s="25" t="n">
+        <v>1346.3</v>
+      </c>
+      <c r="J3" s="25" t="n">
+        <v>249.3</v>
+      </c>
+      <c r="K3" s="25" t="n">
+        <v>1595.6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>stablelm_abl_went_001</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C4" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D4" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>59.84</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>62.06</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>87.97</v>
+      </c>
+      <c r="I4" s="27" t="n">
+        <v>1365.5</v>
+      </c>
+      <c r="J4" s="27" t="n">
+        <v>243.6</v>
+      </c>
+      <c r="K4" s="27" t="n">
+        <v>1609.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>stablelm_abl_went_01</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>49.84</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>88.31999999999999</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>1363</v>
+      </c>
+      <c r="J5" s="27" t="n">
+        <v>231.4</v>
+      </c>
+      <c r="K5" s="27" t="n">
+        <v>1594.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>stablelm_abl_lam_001_w001</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>59.63</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>50.07</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>61.85</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>1355.4</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>231.1</v>
+      </c>
+      <c r="K6" s="27" t="n">
+        <v>1586.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>stablelm_abl_lam_001_w01</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>60.69</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>61.74</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>88.11</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>1361.7</v>
+      </c>
+      <c r="J7" s="27" t="n">
+        <v>246.1</v>
+      </c>
+      <c r="K7" s="27" t="n">
+        <v>1607.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>stablelm_abl_lam_1_w001</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>61.98</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>1364.5</v>
+      </c>
+      <c r="J8" s="27" t="n">
+        <v>227.1</v>
+      </c>
+      <c r="K8" s="27" t="n">
+        <v>1591.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>stablelm_abl_lam_1_w01</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>88.34999999999999</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>1380.6</v>
+      </c>
+      <c r="J9" s="27" t="n">
+        <v>263.9</v>
+      </c>
+      <c r="K9" s="27" t="n">
+        <v>1644.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>stablelm_abl_wbal_0_w001</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C10" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>88.20999999999999</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>1361.4</v>
+      </c>
+      <c r="J10" s="27" t="n">
+        <v>221.1</v>
+      </c>
+      <c r="K10" s="27" t="n">
+        <v>1582.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>stablelm_abl_wbal_0_w01</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>49.82</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>62.01</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>87.94</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>1367.2</v>
+      </c>
+      <c r="J11" s="27" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>1600.8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>stablelm_abl_wbal_01_w001</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>stablelm_abl_wbal_01_w01</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>50.18</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>61.96</v>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>87.87</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>1356.2</v>
+      </c>
+      <c r="J13" s="27" t="n">
+        <v>234.3</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>1590.5</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Colour legend:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>Ablation baseline (already in Main Variants sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Eval pending (running)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Loss formula:  Total = w_ent × (L_leak + lambda × L_imbal) + w_bal × L_var</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>Args:  --entropy_loss_weight (w_ent)  --imbal_lam (lambda)  --balance_loss_weight (w_bal)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>